--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:42</t>
+    <t xml:space="preserve">2026-09-09 22:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:29</t>
+    <t xml:space="preserve">2026-09-12 19:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_tarapaca.xlsx
@@ -36,24 +36,24 @@
     <t xml:space="preserve">Tarapacá</t>
   </si>
   <si>
+    <t xml:space="preserve">Alto Hospicio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pozo Almonte</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pica</t>
   </si>
   <si>
-    <t xml:space="preserve">Pozo Almonte</t>
+    <t xml:space="preserve">Huara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camiña</t>
   </si>
   <si>
     <t xml:space="preserve">Colchane</t>
   </si>
   <si>
-    <t xml:space="preserve">Huara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camiña</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alto Hospicio</t>
-  </si>
-  <si>
     <t xml:space="preserve">Iquique</t>
   </si>
   <si>
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:45</t>
+    <t xml:space="preserve">2026-09-24 00:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -490,13 +490,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1405</v>
+        <v>1107</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>445</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="3">
@@ -513,7 +513,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>393</v>
+        <v>714</v>
       </c>
     </row>
     <row r="4">
@@ -524,13 +524,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>187</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5">
@@ -547,7 +547,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>98</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
@@ -564,7 +564,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-54</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -575,13 +575,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1107</v>
+        <v>1403</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-1979</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -598,7 +598,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-7175</v>
+        <v>-796</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:23</t>
+    <t xml:space="preserve">2026-09-27 22:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:12</t>
+    <t xml:space="preserve">2026-10-01 20:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:52</t>
+    <t xml:space="preserve">2026-10-02 13:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:16</t>
+    <t xml:space="preserve">2026-10-05 07:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
